--- a/rate-tool/data/Cheatsheet.xlsx
+++ b/rate-tool/data/Cheatsheet.xlsx
@@ -17,8 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -104,7 +105,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -128,6 +129,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -916,15 +920,13 @@
         <v>46112</v>
       </c>
       <c r="Y5" s="1" t="n"/>
-      <c r="AA5" s="9" t="n">
-        <v>1650</v>
-      </c>
-      <c r="AB5" s="9" t="n">
-        <v>1800</v>
-      </c>
-      <c r="AC5" s="9" t="n">
-        <v>1800</v>
-      </c>
+      <c r="AA5" s="13" t="n">
+        <v>46082</v>
+      </c>
+      <c r="AB5" s="13" t="n">
+        <v>46112</v>
+      </c>
+      <c r="AC5" s="9" t="n"/>
       <c r="AD5" s="9">
         <f>T5-AA5</f>
         <v/>
@@ -1004,15 +1006,13 @@
         <v>46112</v>
       </c>
       <c r="Y6" s="1" t="n"/>
-      <c r="AA6" s="9" t="n">
-        <v>1650</v>
-      </c>
-      <c r="AB6" s="9" t="n">
-        <v>1800</v>
-      </c>
-      <c r="AC6" s="9" t="n">
-        <v>1800</v>
-      </c>
+      <c r="AA6" s="13" t="n">
+        <v>46082</v>
+      </c>
+      <c r="AB6" s="13" t="n">
+        <v>46112</v>
+      </c>
+      <c r="AC6" s="9" t="n"/>
       <c r="AD6" s="9">
         <f>T6-AA6</f>
         <v/>
@@ -1092,15 +1092,13 @@
         <v>46112</v>
       </c>
       <c r="Y7" s="1" t="n"/>
-      <c r="AA7" s="9" t="n">
-        <v>1650</v>
-      </c>
-      <c r="AB7" s="9" t="n">
-        <v>1800</v>
-      </c>
-      <c r="AC7" s="9" t="n">
-        <v>1800</v>
-      </c>
+      <c r="AA7" s="13" t="n">
+        <v>46082</v>
+      </c>
+      <c r="AB7" s="13" t="n">
+        <v>46112</v>
+      </c>
+      <c r="AC7" s="9" t="n"/>
       <c r="AD7" s="9">
         <f>T7-AA7</f>
         <v/>
@@ -1186,15 +1184,13 @@
         <v>46112</v>
       </c>
       <c r="Y8" s="1" t="n"/>
-      <c r="AA8" s="9" t="n">
-        <v>1650</v>
-      </c>
-      <c r="AB8" s="9" t="n">
-        <v>1800</v>
-      </c>
-      <c r="AC8" s="9" t="n">
-        <v>1800</v>
-      </c>
+      <c r="AA8" s="13" t="n">
+        <v>46082</v>
+      </c>
+      <c r="AB8" s="13" t="n">
+        <v>46112</v>
+      </c>
+      <c r="AC8" s="9" t="n"/>
       <c r="AD8" s="9">
         <f>T8-AA8</f>
         <v/>
@@ -1280,15 +1276,13 @@
         <v>46112</v>
       </c>
       <c r="Y9" s="1" t="n"/>
-      <c r="AA9" s="9" t="n">
-        <v>1650</v>
-      </c>
-      <c r="AB9" s="9" t="n">
-        <v>1800</v>
-      </c>
-      <c r="AC9" s="9" t="n">
-        <v>1800</v>
-      </c>
+      <c r="AA9" s="13" t="n">
+        <v>46082</v>
+      </c>
+      <c r="AB9" s="13" t="n">
+        <v>46112</v>
+      </c>
+      <c r="AC9" s="9" t="n"/>
       <c r="AD9" s="9">
         <f>T9-AA9</f>
         <v/>
@@ -1368,15 +1362,13 @@
         <v>46112</v>
       </c>
       <c r="Y10" s="1" t="n"/>
-      <c r="AA10" s="9" t="n">
-        <v>1350</v>
-      </c>
-      <c r="AB10" s="9" t="n">
-        <v>1550</v>
-      </c>
-      <c r="AC10" s="9" t="n">
-        <v>1550</v>
-      </c>
+      <c r="AA10" s="13" t="n">
+        <v>46082</v>
+      </c>
+      <c r="AB10" s="13" t="n">
+        <v>46112</v>
+      </c>
+      <c r="AC10" s="9" t="n"/>
       <c r="AD10" s="9">
         <f>T10-AA10</f>
         <v/>
@@ -1456,15 +1448,13 @@
         <v>46112</v>
       </c>
       <c r="Y11" s="1" t="n"/>
-      <c r="AA11" s="9" t="n">
-        <v>1350</v>
-      </c>
-      <c r="AB11" s="9" t="n">
-        <v>1550</v>
-      </c>
-      <c r="AC11" s="9" t="n">
-        <v>1550</v>
-      </c>
+      <c r="AA11" s="13" t="n">
+        <v>46082</v>
+      </c>
+      <c r="AB11" s="13" t="n">
+        <v>46112</v>
+      </c>
+      <c r="AC11" s="9" t="n"/>
       <c r="AD11" s="9">
         <f>T11-AA11</f>
         <v/>
@@ -1547,18 +1537,13 @@
         <v>46112</v>
       </c>
       <c r="Y12" s="1" t="n"/>
-      <c r="AA12" s="9">
-        <f>H5</f>
-        <v/>
-      </c>
-      <c r="AB12" s="9">
-        <f>I5</f>
-        <v/>
-      </c>
-      <c r="AC12" s="9">
-        <f>J5</f>
-        <v/>
-      </c>
+      <c r="AA12" s="13" t="n">
+        <v>46082</v>
+      </c>
+      <c r="AB12" s="13" t="n">
+        <v>46112</v>
+      </c>
+      <c r="AC12" s="9" t="n"/>
       <c r="AD12" s="9">
         <f>T12-AA12</f>
         <v/>
@@ -1641,18 +1626,13 @@
         <v>46112</v>
       </c>
       <c r="Y13" s="1" t="n"/>
-      <c r="AA13" s="9">
-        <f>H6</f>
-        <v/>
-      </c>
-      <c r="AB13" s="9">
-        <f>I6</f>
-        <v/>
-      </c>
-      <c r="AC13" s="9">
-        <f>J6</f>
-        <v/>
-      </c>
+      <c r="AA13" s="13" t="n">
+        <v>46082</v>
+      </c>
+      <c r="AB13" s="13" t="n">
+        <v>46112</v>
+      </c>
+      <c r="AC13" s="9" t="n"/>
       <c r="AD13" s="9">
         <f>T13-AA13</f>
         <v/>
@@ -1735,18 +1715,13 @@
         <v>46112</v>
       </c>
       <c r="Y14" s="1" t="n"/>
-      <c r="AA14" s="9">
-        <f>H7</f>
-        <v/>
-      </c>
-      <c r="AB14" s="9">
-        <f>I7</f>
-        <v/>
-      </c>
-      <c r="AC14" s="9">
-        <f>J7</f>
-        <v/>
-      </c>
+      <c r="AA14" s="13" t="n">
+        <v>46082</v>
+      </c>
+      <c r="AB14" s="13" t="n">
+        <v>46112</v>
+      </c>
+      <c r="AC14" s="9" t="n"/>
       <c r="AD14" s="9">
         <f>T14-AA14</f>
         <v/>
@@ -1835,18 +1810,13 @@
         <v>46112</v>
       </c>
       <c r="Y15" s="1" t="n"/>
-      <c r="AA15" s="9">
-        <f>H8</f>
-        <v/>
-      </c>
-      <c r="AB15" s="9">
-        <f>I8</f>
-        <v/>
-      </c>
-      <c r="AC15" s="9">
-        <f>J8</f>
-        <v/>
-      </c>
+      <c r="AA15" s="13" t="n">
+        <v>46082</v>
+      </c>
+      <c r="AB15" s="13" t="n">
+        <v>46112</v>
+      </c>
+      <c r="AC15" s="9" t="n"/>
       <c r="AD15" s="9">
         <f>T15-AA15</f>
         <v/>
@@ -1935,18 +1905,13 @@
         <v>46112</v>
       </c>
       <c r="Y16" s="1" t="n"/>
-      <c r="AA16" s="9">
-        <f>H9</f>
-        <v/>
-      </c>
-      <c r="AB16" s="9">
-        <f>I9</f>
-        <v/>
-      </c>
-      <c r="AC16" s="9">
-        <f>J9</f>
-        <v/>
-      </c>
+      <c r="AA16" s="13" t="n">
+        <v>46082</v>
+      </c>
+      <c r="AB16" s="13" t="n">
+        <v>46112</v>
+      </c>
+      <c r="AC16" s="9" t="n"/>
       <c r="AD16" s="9">
         <f>T16-AA16</f>
         <v/>
@@ -2029,18 +1994,13 @@
         <v>46112</v>
       </c>
       <c r="Y17" s="1" t="n"/>
-      <c r="AA17" s="9">
-        <f>H10</f>
-        <v/>
-      </c>
-      <c r="AB17" s="9">
-        <f>I10</f>
-        <v/>
-      </c>
-      <c r="AC17" s="9">
-        <f>J10</f>
-        <v/>
-      </c>
+      <c r="AA17" s="13" t="n">
+        <v>46082</v>
+      </c>
+      <c r="AB17" s="13" t="n">
+        <v>46112</v>
+      </c>
+      <c r="AC17" s="9" t="n"/>
       <c r="AD17" s="9">
         <f>T17-AA17</f>
         <v/>
@@ -2123,18 +2083,13 @@
         <v>46112</v>
       </c>
       <c r="Y18" s="1" t="n"/>
-      <c r="AA18" s="9">
-        <f>H11</f>
-        <v/>
-      </c>
-      <c r="AB18" s="9">
-        <f>I11</f>
-        <v/>
-      </c>
-      <c r="AC18" s="9">
-        <f>J11</f>
-        <v/>
-      </c>
+      <c r="AA18" s="13" t="n">
+        <v>46082</v>
+      </c>
+      <c r="AB18" s="13" t="n">
+        <v>46112</v>
+      </c>
+      <c r="AC18" s="9" t="n"/>
       <c r="AD18" s="9">
         <f>T18-AA18</f>
         <v/>
@@ -2217,18 +2172,13 @@
         <v>46112</v>
       </c>
       <c r="Y19" s="1" t="n"/>
-      <c r="AA19" s="9">
-        <f>H5</f>
-        <v/>
-      </c>
-      <c r="AB19" s="9">
-        <f>I5</f>
-        <v/>
-      </c>
-      <c r="AC19" s="9">
-        <f>J5</f>
-        <v/>
-      </c>
+      <c r="AA19" s="13" t="n">
+        <v>46082</v>
+      </c>
+      <c r="AB19" s="13" t="n">
+        <v>46112</v>
+      </c>
+      <c r="AC19" s="9" t="n"/>
       <c r="AD19" s="9">
         <f>T19-AA19</f>
         <v/>
@@ -2311,18 +2261,13 @@
         <v>46112</v>
       </c>
       <c r="Y20" s="1" t="n"/>
-      <c r="AA20" s="9">
-        <f>H6</f>
-        <v/>
-      </c>
-      <c r="AB20" s="9">
-        <f>I6</f>
-        <v/>
-      </c>
-      <c r="AC20" s="9">
-        <f>J6</f>
-        <v/>
-      </c>
+      <c r="AA20" s="13" t="n">
+        <v>46082</v>
+      </c>
+      <c r="AB20" s="13" t="n">
+        <v>46112</v>
+      </c>
+      <c r="AC20" s="9" t="n"/>
       <c r="AD20" s="9">
         <f>T20-AA20</f>
         <v/>
@@ -2405,18 +2350,13 @@
         <v>46112</v>
       </c>
       <c r="Y21" s="1" t="n"/>
-      <c r="AA21" s="9">
-        <f>H7</f>
-        <v/>
-      </c>
-      <c r="AB21" s="9">
-        <f>I7</f>
-        <v/>
-      </c>
-      <c r="AC21" s="9">
-        <f>J7</f>
-        <v/>
-      </c>
+      <c r="AA21" s="13" t="n">
+        <v>46082</v>
+      </c>
+      <c r="AB21" s="13" t="n">
+        <v>46112</v>
+      </c>
+      <c r="AC21" s="9" t="n"/>
       <c r="AD21" s="9">
         <f>T21-AA21</f>
         <v/>
@@ -2505,18 +2445,13 @@
         <v>46112</v>
       </c>
       <c r="Y22" s="1" t="n"/>
-      <c r="AA22" s="9">
-        <f>H8</f>
-        <v/>
-      </c>
-      <c r="AB22" s="9">
-        <f>I8</f>
-        <v/>
-      </c>
-      <c r="AC22" s="9">
-        <f>J8</f>
-        <v/>
-      </c>
+      <c r="AA22" s="13" t="n">
+        <v>46082</v>
+      </c>
+      <c r="AB22" s="13" t="n">
+        <v>46112</v>
+      </c>
+      <c r="AC22" s="9" t="n"/>
       <c r="AD22" s="9">
         <f>T22-AA22</f>
         <v/>
@@ -2605,18 +2540,13 @@
         <v>46112</v>
       </c>
       <c r="Y23" s="1" t="n"/>
-      <c r="AA23" s="9">
-        <f>H9</f>
-        <v/>
-      </c>
-      <c r="AB23" s="9">
-        <f>I9</f>
-        <v/>
-      </c>
-      <c r="AC23" s="9">
-        <f>J9</f>
-        <v/>
-      </c>
+      <c r="AA23" s="13" t="n">
+        <v>46082</v>
+      </c>
+      <c r="AB23" s="13" t="n">
+        <v>46112</v>
+      </c>
+      <c r="AC23" s="9" t="n"/>
       <c r="AD23" s="9">
         <f>T23-AA23</f>
         <v/>
@@ -2699,18 +2629,13 @@
         <v>46112</v>
       </c>
       <c r="Y24" s="1" t="n"/>
-      <c r="AA24" s="9">
-        <f>H10</f>
-        <v/>
-      </c>
-      <c r="AB24" s="9">
-        <f>I10</f>
-        <v/>
-      </c>
-      <c r="AC24" s="9">
-        <f>J10</f>
-        <v/>
-      </c>
+      <c r="AA24" s="13" t="n">
+        <v>46082</v>
+      </c>
+      <c r="AB24" s="13" t="n">
+        <v>46112</v>
+      </c>
+      <c r="AC24" s="9" t="n"/>
       <c r="AD24" s="9">
         <f>T24-AA24</f>
         <v/>
@@ -2793,18 +2718,13 @@
         <v>46112</v>
       </c>
       <c r="Y25" s="1" t="n"/>
-      <c r="AA25" s="9">
-        <f>H11</f>
-        <v/>
-      </c>
-      <c r="AB25" s="9">
-        <f>I11</f>
-        <v/>
-      </c>
-      <c r="AC25" s="9">
-        <f>J11</f>
-        <v/>
-      </c>
+      <c r="AA25" s="13" t="n">
+        <v>46082</v>
+      </c>
+      <c r="AB25" s="13" t="n">
+        <v>46112</v>
+      </c>
+      <c r="AC25" s="9" t="n"/>
       <c r="AD25" s="9">
         <f>T25-AA25</f>
         <v/>
@@ -2890,15 +2810,13 @@
         <v>46112</v>
       </c>
       <c r="Y26" s="1" t="n"/>
-      <c r="AA26" s="9" t="n">
-        <v>2000</v>
-      </c>
-      <c r="AB26" s="9" t="n">
-        <v>2100</v>
-      </c>
-      <c r="AC26" s="9" t="n">
-        <v>2100</v>
-      </c>
+      <c r="AA26" s="13" t="n">
+        <v>46082</v>
+      </c>
+      <c r="AB26" s="13" t="n">
+        <v>46112</v>
+      </c>
+      <c r="AC26" s="9" t="n"/>
       <c r="AD26" s="9">
         <f>T26-AA26</f>
         <v/>
@@ -2978,15 +2896,13 @@
         <v>46112</v>
       </c>
       <c r="Y27" s="1" t="n"/>
-      <c r="AA27" s="9" t="n">
-        <v>2000</v>
-      </c>
-      <c r="AB27" s="9" t="n">
-        <v>2100</v>
-      </c>
-      <c r="AC27" s="9" t="n">
-        <v>2100</v>
-      </c>
+      <c r="AA27" s="13" t="n">
+        <v>46082</v>
+      </c>
+      <c r="AB27" s="13" t="n">
+        <v>46112</v>
+      </c>
+      <c r="AC27" s="9" t="n"/>
       <c r="AD27" s="9">
         <f>T27-AA27</f>
         <v/>
@@ -3066,15 +2982,13 @@
         <v>46112</v>
       </c>
       <c r="Y28" s="1" t="n"/>
-      <c r="AA28" s="9" t="n">
-        <v>2000</v>
-      </c>
-      <c r="AB28" s="9" t="n">
-        <v>2100</v>
-      </c>
-      <c r="AC28" s="9" t="n">
-        <v>2100</v>
-      </c>
+      <c r="AA28" s="13" t="n">
+        <v>46082</v>
+      </c>
+      <c r="AB28" s="13" t="n">
+        <v>46112</v>
+      </c>
+      <c r="AC28" s="9" t="n"/>
       <c r="AD28" s="9">
         <f>T28-AA28</f>
         <v/>
@@ -3163,18 +3077,13 @@
         <v>46112</v>
       </c>
       <c r="Y29" s="1" t="n"/>
-      <c r="AA29" s="9">
-        <f>H26</f>
-        <v/>
-      </c>
-      <c r="AB29" s="9">
-        <f>I26</f>
-        <v/>
-      </c>
-      <c r="AC29" s="9">
-        <f>J26</f>
-        <v/>
-      </c>
+      <c r="AA29" s="13" t="n">
+        <v>46082</v>
+      </c>
+      <c r="AB29" s="13" t="n">
+        <v>46112</v>
+      </c>
+      <c r="AC29" s="9" t="n"/>
       <c r="AD29" s="9">
         <f>T29-AA29</f>
         <v/>
@@ -3257,18 +3166,13 @@
         <v>46112</v>
       </c>
       <c r="Y30" s="1" t="n"/>
-      <c r="AA30" s="9">
-        <f>H27</f>
-        <v/>
-      </c>
-      <c r="AB30" s="9">
-        <f>I27</f>
-        <v/>
-      </c>
-      <c r="AC30" s="9">
-        <f>J27</f>
-        <v/>
-      </c>
+      <c r="AA30" s="13" t="n">
+        <v>46082</v>
+      </c>
+      <c r="AB30" s="13" t="n">
+        <v>46112</v>
+      </c>
+      <c r="AC30" s="9" t="n"/>
       <c r="AD30" s="9">
         <f>T30-AA30</f>
         <v/>
@@ -3351,18 +3255,13 @@
         <v>46112</v>
       </c>
       <c r="Y31" s="1" t="n"/>
-      <c r="AA31" s="9">
-        <f>H28</f>
-        <v/>
-      </c>
-      <c r="AB31" s="9">
-        <f>I28</f>
-        <v/>
-      </c>
-      <c r="AC31" s="9">
-        <f>J28</f>
-        <v/>
-      </c>
+      <c r="AA31" s="13" t="n">
+        <v>46082</v>
+      </c>
+      <c r="AB31" s="13" t="n">
+        <v>46112</v>
+      </c>
+      <c r="AC31" s="9" t="n"/>
       <c r="AD31" s="9">
         <f>T31-AA31</f>
         <v/>
@@ -3451,18 +3350,13 @@
         <v>46112</v>
       </c>
       <c r="Y32" s="1" t="n"/>
-      <c r="AA32" s="9">
-        <f>H26</f>
-        <v/>
-      </c>
-      <c r="AB32" s="9">
-        <f>I26</f>
-        <v/>
-      </c>
-      <c r="AC32" s="9">
-        <f>J26</f>
-        <v/>
-      </c>
+      <c r="AA32" s="13" t="n">
+        <v>46082</v>
+      </c>
+      <c r="AB32" s="13" t="n">
+        <v>46112</v>
+      </c>
+      <c r="AC32" s="9" t="n"/>
       <c r="AD32" s="9">
         <f>T32-AA32</f>
         <v/>
@@ -3545,18 +3439,13 @@
         <v>46112</v>
       </c>
       <c r="Y33" s="1" t="n"/>
-      <c r="AA33" s="9">
-        <f>H27</f>
-        <v/>
-      </c>
-      <c r="AB33" s="9">
-        <f>I27</f>
-        <v/>
-      </c>
-      <c r="AC33" s="9">
-        <f>J27</f>
-        <v/>
-      </c>
+      <c r="AA33" s="13" t="n">
+        <v>46082</v>
+      </c>
+      <c r="AB33" s="13" t="n">
+        <v>46112</v>
+      </c>
+      <c r="AC33" s="9" t="n"/>
       <c r="AD33" s="9">
         <f>T33-AA33</f>
         <v/>
@@ -3639,18 +3528,13 @@
         <v>46112</v>
       </c>
       <c r="Y34" s="1" t="n"/>
-      <c r="AA34" s="9">
-        <f>H28</f>
-        <v/>
-      </c>
-      <c r="AB34" s="9">
-        <f>I28</f>
-        <v/>
-      </c>
-      <c r="AC34" s="9">
-        <f>J28</f>
-        <v/>
-      </c>
+      <c r="AA34" s="13" t="n">
+        <v>46082</v>
+      </c>
+      <c r="AB34" s="13" t="n">
+        <v>46112</v>
+      </c>
+      <c r="AC34" s="9" t="n"/>
       <c r="AD34" s="9">
         <f>T34-AA34</f>
         <v/>
@@ -3764,18 +3648,13 @@
         <v>46112</v>
       </c>
       <c r="Y35" s="5" t="n"/>
-      <c r="AA35" s="9">
-        <f>VLOOKUP($A35,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AB35" s="9">
-        <f>VLOOKUP($A35,$A$5:$J$34,9,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AC35" s="9">
-        <f>VLOOKUP($A35,$A$5:$J$34,10,FALSE)</f>
-        <v/>
-      </c>
+      <c r="AA35" s="13" t="n">
+        <v>46082</v>
+      </c>
+      <c r="AB35" s="13" t="n">
+        <v>46112</v>
+      </c>
+      <c r="AC35" s="9" t="n"/>
       <c r="AD35" s="9">
         <f>T35-AA35</f>
         <v/>
@@ -3889,18 +3768,13 @@
         <v>46112</v>
       </c>
       <c r="Y36" s="5" t="n"/>
-      <c r="AA36" s="9">
-        <f>VLOOKUP($A36,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AB36" s="9">
-        <f>VLOOKUP($A36,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AC36" s="9">
-        <f>VLOOKUP($A36,$A$5:$J$34,9,FALSE)</f>
-        <v/>
-      </c>
+      <c r="AA36" s="13" t="n">
+        <v>46082</v>
+      </c>
+      <c r="AB36" s="13" t="n">
+        <v>46112</v>
+      </c>
+      <c r="AC36" s="9" t="n"/>
       <c r="AD36" s="9">
         <f>T36-AA36</f>
         <v/>
@@ -4014,18 +3888,13 @@
         <v>46112</v>
       </c>
       <c r="Y37" s="5" t="n"/>
-      <c r="AA37" s="9">
-        <f>VLOOKUP($A37,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AB37" s="9">
-        <f>VLOOKUP($A37,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AC37" s="9">
-        <f>VLOOKUP($A37,$A$5:$J$34,9,FALSE)</f>
-        <v/>
-      </c>
+      <c r="AA37" s="13" t="n">
+        <v>46082</v>
+      </c>
+      <c r="AB37" s="13" t="n">
+        <v>46112</v>
+      </c>
+      <c r="AC37" s="9" t="n"/>
       <c r="AD37" s="9">
         <f>T37-AA37</f>
         <v/>
@@ -4139,18 +4008,13 @@
         <v>46112</v>
       </c>
       <c r="Y38" s="5" t="n"/>
-      <c r="AA38" s="9">
-        <f>VLOOKUP($A38,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AB38" s="9">
-        <f>VLOOKUP($A38,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AC38" s="9">
-        <f>VLOOKUP($A38,$A$5:$J$34,9,FALSE)</f>
-        <v/>
-      </c>
+      <c r="AA38" s="13" t="n">
+        <v>46082</v>
+      </c>
+      <c r="AB38" s="13" t="n">
+        <v>46112</v>
+      </c>
+      <c r="AC38" s="9" t="n"/>
       <c r="AD38" s="9">
         <f>T38-AA38</f>
         <v/>
@@ -4264,18 +4128,13 @@
         <v>46112</v>
       </c>
       <c r="Y39" s="5" t="n"/>
-      <c r="AA39" s="9">
-        <f>VLOOKUP($A39,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AB39" s="9">
-        <f>VLOOKUP($A39,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AC39" s="9">
-        <f>VLOOKUP($A39,$A$5:$J$34,9,FALSE)</f>
-        <v/>
-      </c>
+      <c r="AA39" s="13" t="n">
+        <v>46082</v>
+      </c>
+      <c r="AB39" s="13" t="n">
+        <v>46112</v>
+      </c>
+      <c r="AC39" s="9" t="n"/>
       <c r="AD39" s="9">
         <f>T39-AA39</f>
         <v/>
@@ -4389,18 +4248,13 @@
         <v>46112</v>
       </c>
       <c r="Y40" s="5" t="n"/>
-      <c r="AA40" s="9">
-        <f>VLOOKUP($A40,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AB40" s="9">
-        <f>VLOOKUP($A40,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AC40" s="9">
-        <f>VLOOKUP($A40,$A$5:$J$34,9,FALSE)</f>
-        <v/>
-      </c>
+      <c r="AA40" s="13" t="n">
+        <v>46082</v>
+      </c>
+      <c r="AB40" s="13" t="n">
+        <v>46112</v>
+      </c>
+      <c r="AC40" s="9" t="n"/>
       <c r="AD40" s="9">
         <f>T40-AA40</f>
         <v/>
@@ -4514,18 +4368,13 @@
         <v>46112</v>
       </c>
       <c r="Y41" s="5" t="n"/>
-      <c r="AA41" s="9">
-        <f>VLOOKUP($A41,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AB41" s="9">
-        <f>VLOOKUP($A41,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AC41" s="9">
-        <f>VLOOKUP($A41,$A$5:$J$34,9,FALSE)</f>
-        <v/>
-      </c>
+      <c r="AA41" s="13" t="n">
+        <v>46082</v>
+      </c>
+      <c r="AB41" s="13" t="n">
+        <v>46112</v>
+      </c>
+      <c r="AC41" s="9" t="n"/>
       <c r="AD41" s="9">
         <f>T41-AA41</f>
         <v/>
@@ -4639,18 +4488,13 @@
         <v>46112</v>
       </c>
       <c r="Y42" s="5" t="n"/>
-      <c r="AA42" s="9">
-        <f>VLOOKUP($A42,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AB42" s="9">
-        <f>VLOOKUP($A42,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AC42" s="9">
-        <f>VLOOKUP($A42,$A$5:$J$34,9,FALSE)</f>
-        <v/>
-      </c>
+      <c r="AA42" s="13" t="n">
+        <v>46082</v>
+      </c>
+      <c r="AB42" s="13" t="n">
+        <v>46112</v>
+      </c>
+      <c r="AC42" s="9" t="n"/>
       <c r="AD42" s="9">
         <f>T42-AA42</f>
         <v/>
@@ -4764,18 +4608,13 @@
         <v>46112</v>
       </c>
       <c r="Y43" s="5" t="n"/>
-      <c r="AA43" s="9">
-        <f>VLOOKUP($A43,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AB43" s="9">
-        <f>VLOOKUP($A43,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AC43" s="9">
-        <f>VLOOKUP($A43,$A$5:$J$34,9,FALSE)</f>
-        <v/>
-      </c>
+      <c r="AA43" s="13" t="n">
+        <v>46082</v>
+      </c>
+      <c r="AB43" s="13" t="n">
+        <v>46112</v>
+      </c>
+      <c r="AC43" s="9" t="n"/>
       <c r="AD43" s="9">
         <f>T43-AA43</f>
         <v/>
@@ -4889,18 +4728,13 @@
         <v>46112</v>
       </c>
       <c r="Y44" s="5" t="n"/>
-      <c r="AA44" s="9">
-        <f>VLOOKUP($A44,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AB44" s="9">
-        <f>VLOOKUP($A44,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AC44" s="9">
-        <f>VLOOKUP($A44,$A$5:$J$34,9,FALSE)</f>
-        <v/>
-      </c>
+      <c r="AA44" s="13" t="n">
+        <v>46082</v>
+      </c>
+      <c r="AB44" s="13" t="n">
+        <v>46112</v>
+      </c>
+      <c r="AC44" s="9" t="n"/>
       <c r="AD44" s="9">
         <f>T44-AA44</f>
         <v/>
@@ -5014,18 +4848,13 @@
         <v>46112</v>
       </c>
       <c r="Y45" s="5" t="n"/>
-      <c r="AA45" s="9">
-        <f>VLOOKUP($A45,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AB45" s="9">
-        <f>VLOOKUP($A45,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AC45" s="9">
-        <f>VLOOKUP($A45,$A$5:$J$34,9,FALSE)</f>
-        <v/>
-      </c>
+      <c r="AA45" s="13" t="n">
+        <v>46082</v>
+      </c>
+      <c r="AB45" s="13" t="n">
+        <v>46112</v>
+      </c>
+      <c r="AC45" s="9" t="n"/>
       <c r="AD45" s="9">
         <f>T45-AA45</f>
         <v/>
@@ -5139,18 +4968,13 @@
         <v>46112</v>
       </c>
       <c r="Y46" s="5" t="n"/>
-      <c r="AA46" s="9">
-        <f>VLOOKUP($A46,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AB46" s="9">
-        <f>VLOOKUP($A46,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AC46" s="9">
-        <f>VLOOKUP($A46,$A$5:$J$34,9,FALSE)</f>
-        <v/>
-      </c>
+      <c r="AA46" s="13" t="n">
+        <v>46082</v>
+      </c>
+      <c r="AB46" s="13" t="n">
+        <v>46112</v>
+      </c>
+      <c r="AC46" s="9" t="n"/>
       <c r="AD46" s="9">
         <f>T46-AA46</f>
         <v/>
@@ -5264,18 +5088,13 @@
         <v>46112</v>
       </c>
       <c r="Y47" s="5" t="n"/>
-      <c r="AA47" s="9">
-        <f>VLOOKUP($A47,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AB47" s="9">
-        <f>VLOOKUP($A47,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AC47" s="9">
-        <f>VLOOKUP($A47,$A$5:$J$34,9,FALSE)</f>
-        <v/>
-      </c>
+      <c r="AA47" s="13" t="n">
+        <v>46082</v>
+      </c>
+      <c r="AB47" s="13" t="n">
+        <v>46112</v>
+      </c>
+      <c r="AC47" s="9" t="n"/>
       <c r="AD47" s="9">
         <f>T47-AA47</f>
         <v/>
@@ -5389,18 +5208,13 @@
         <v>46112</v>
       </c>
       <c r="Y48" s="5" t="n"/>
-      <c r="AA48" s="9">
-        <f>VLOOKUP($A48,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AB48" s="9">
-        <f>VLOOKUP($A48,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AC48" s="9">
-        <f>VLOOKUP($A48,$A$5:$J$34,9,FALSE)</f>
-        <v/>
-      </c>
+      <c r="AA48" s="13" t="n">
+        <v>46082</v>
+      </c>
+      <c r="AB48" s="13" t="n">
+        <v>46112</v>
+      </c>
+      <c r="AC48" s="9" t="n"/>
       <c r="AD48" s="9">
         <f>T48-AA48</f>
         <v/>
@@ -5514,18 +5328,13 @@
         <v>46112</v>
       </c>
       <c r="Y49" s="5" t="n"/>
-      <c r="AA49" s="9">
-        <f>VLOOKUP($A49,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AB49" s="9">
-        <f>VLOOKUP($A49,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AC49" s="9">
-        <f>VLOOKUP($A49,$A$5:$J$34,9,FALSE)</f>
-        <v/>
-      </c>
+      <c r="AA49" s="13" t="n">
+        <v>46082</v>
+      </c>
+      <c r="AB49" s="13" t="n">
+        <v>46112</v>
+      </c>
+      <c r="AC49" s="9" t="n"/>
       <c r="AD49" s="9">
         <f>T49-AA49</f>
         <v/>
@@ -5639,18 +5448,13 @@
         <v>46112</v>
       </c>
       <c r="Y50" s="5" t="n"/>
-      <c r="AA50" s="9">
-        <f>VLOOKUP($A50,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AB50" s="9">
-        <f>VLOOKUP($A50,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AC50" s="9">
-        <f>VLOOKUP($A50,$A$5:$J$34,9,FALSE)</f>
-        <v/>
-      </c>
+      <c r="AA50" s="13" t="n">
+        <v>46082</v>
+      </c>
+      <c r="AB50" s="13" t="n">
+        <v>46112</v>
+      </c>
+      <c r="AC50" s="9" t="n"/>
       <c r="AD50" s="9">
         <f>T50-AA50</f>
         <v/>
@@ -5764,18 +5568,13 @@
         <v>46112</v>
       </c>
       <c r="Y51" s="5" t="n"/>
-      <c r="AA51" s="9">
-        <f>VLOOKUP($A51,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AB51" s="9">
-        <f>VLOOKUP($A51,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AC51" s="9">
-        <f>VLOOKUP($A51,$A$5:$J$34,9,FALSE)</f>
-        <v/>
-      </c>
+      <c r="AA51" s="13" t="n">
+        <v>46082</v>
+      </c>
+      <c r="AB51" s="13" t="n">
+        <v>46112</v>
+      </c>
+      <c r="AC51" s="9" t="n"/>
       <c r="AD51" s="9">
         <f>T51-AA51</f>
         <v/>
@@ -5889,18 +5688,13 @@
         <v>46112</v>
       </c>
       <c r="Y52" s="5" t="n"/>
-      <c r="AA52" s="9">
-        <f>VLOOKUP($A52,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AB52" s="9">
-        <f>VLOOKUP($A52,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AC52" s="9">
-        <f>VLOOKUP($A52,$A$5:$J$34,9,FALSE)</f>
-        <v/>
-      </c>
+      <c r="AA52" s="13" t="n">
+        <v>46082</v>
+      </c>
+      <c r="AB52" s="13" t="n">
+        <v>46112</v>
+      </c>
+      <c r="AC52" s="9" t="n"/>
       <c r="AD52" s="9">
         <f>T52-AA52</f>
         <v/>
@@ -6014,18 +5808,13 @@
         <v>46112</v>
       </c>
       <c r="Y53" s="5" t="n"/>
-      <c r="AA53" s="9">
-        <f>VLOOKUP($A53,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AB53" s="9">
-        <f>VLOOKUP($A53,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AC53" s="9">
-        <f>VLOOKUP($A53,$A$5:$J$34,9,FALSE)</f>
-        <v/>
-      </c>
+      <c r="AA53" s="13" t="n">
+        <v>46082</v>
+      </c>
+      <c r="AB53" s="13" t="n">
+        <v>46112</v>
+      </c>
+      <c r="AC53" s="9" t="n"/>
       <c r="AD53" s="9">
         <f>T53-AA53</f>
         <v/>
@@ -6139,18 +5928,13 @@
         <v>46112</v>
       </c>
       <c r="Y54" s="5" t="n"/>
-      <c r="AA54" s="9">
-        <f>VLOOKUP($A54,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AB54" s="9">
-        <f>VLOOKUP($A54,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AC54" s="9">
-        <f>VLOOKUP($A54,$A$5:$J$34,9,FALSE)</f>
-        <v/>
-      </c>
+      <c r="AA54" s="13" t="n">
+        <v>46082</v>
+      </c>
+      <c r="AB54" s="13" t="n">
+        <v>46112</v>
+      </c>
+      <c r="AC54" s="9" t="n"/>
       <c r="AD54" s="9">
         <f>T54-AA54</f>
         <v/>
@@ -6264,18 +6048,13 @@
         <v>46112</v>
       </c>
       <c r="Y55" s="5" t="n"/>
-      <c r="AA55" s="9">
-        <f>VLOOKUP($A55,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AB55" s="9">
-        <f>VLOOKUP($A55,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AC55" s="9">
-        <f>VLOOKUP($A55,$A$5:$J$34,9,FALSE)</f>
-        <v/>
-      </c>
+      <c r="AA55" s="13" t="n">
+        <v>46082</v>
+      </c>
+      <c r="AB55" s="13" t="n">
+        <v>46112</v>
+      </c>
+      <c r="AC55" s="9" t="n"/>
       <c r="AD55" s="9">
         <f>T55-AA55</f>
         <v/>
@@ -6389,18 +6168,13 @@
         <v>46112</v>
       </c>
       <c r="Y56" s="5" t="n"/>
-      <c r="AA56" s="9">
-        <f>VLOOKUP($A56,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AB56" s="9">
-        <f>VLOOKUP($A56,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AC56" s="9">
-        <f>VLOOKUP($A56,$A$5:$J$34,9,FALSE)</f>
-        <v/>
-      </c>
+      <c r="AA56" s="13" t="n">
+        <v>46082</v>
+      </c>
+      <c r="AB56" s="13" t="n">
+        <v>46112</v>
+      </c>
+      <c r="AC56" s="9" t="n"/>
       <c r="AD56" s="9">
         <f>T56-AA56</f>
         <v/>
@@ -6514,18 +6288,13 @@
         <v>46112</v>
       </c>
       <c r="Y57" s="5" t="n"/>
-      <c r="AA57" s="9">
-        <f>VLOOKUP($A57,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AB57" s="9">
-        <f>VLOOKUP($A57,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AC57" s="9">
-        <f>VLOOKUP($A57,$A$5:$J$34,9,FALSE)</f>
-        <v/>
-      </c>
+      <c r="AA57" s="13" t="n">
+        <v>46082</v>
+      </c>
+      <c r="AB57" s="13" t="n">
+        <v>46112</v>
+      </c>
+      <c r="AC57" s="9" t="n"/>
       <c r="AD57" s="9">
         <f>T57-AA57</f>
         <v/>
@@ -6639,18 +6408,13 @@
         <v>46112</v>
       </c>
       <c r="Y58" s="5" t="n"/>
-      <c r="AA58" s="9">
-        <f>VLOOKUP($A58,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AB58" s="9">
-        <f>VLOOKUP($A58,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AC58" s="9">
-        <f>VLOOKUP($A58,$A$5:$J$34,9,FALSE)</f>
-        <v/>
-      </c>
+      <c r="AA58" s="13" t="n">
+        <v>46082</v>
+      </c>
+      <c r="AB58" s="13" t="n">
+        <v>46112</v>
+      </c>
+      <c r="AC58" s="9" t="n"/>
       <c r="AD58" s="9">
         <f>T58-AA58</f>
         <v/>
@@ -6764,18 +6528,13 @@
         <v>46112</v>
       </c>
       <c r="Y59" s="5" t="n"/>
-      <c r="AA59" s="9">
-        <f>VLOOKUP($A59,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AB59" s="9">
-        <f>VLOOKUP($A59,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AC59" s="9">
-        <f>VLOOKUP($A59,$A$5:$J$34,9,FALSE)</f>
-        <v/>
-      </c>
+      <c r="AA59" s="13" t="n">
+        <v>46082</v>
+      </c>
+      <c r="AB59" s="13" t="n">
+        <v>46112</v>
+      </c>
+      <c r="AC59" s="9" t="n"/>
       <c r="AD59" s="9">
         <f>T59-AA59</f>
         <v/>
@@ -6889,18 +6648,13 @@
         <v>46112</v>
       </c>
       <c r="Y60" s="5" t="n"/>
-      <c r="AA60" s="9">
-        <f>VLOOKUP($A60,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AB60" s="9">
-        <f>VLOOKUP($A60,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AC60" s="9">
-        <f>VLOOKUP($A60,$A$5:$J$34,9,FALSE)</f>
-        <v/>
-      </c>
+      <c r="AA60" s="13" t="n">
+        <v>46082</v>
+      </c>
+      <c r="AB60" s="13" t="n">
+        <v>46112</v>
+      </c>
+      <c r="AC60" s="9" t="n"/>
       <c r="AD60" s="9">
         <f>T60-AA60</f>
         <v/>
@@ -7014,18 +6768,13 @@
         <v>46112</v>
       </c>
       <c r="Y61" s="5" t="n"/>
-      <c r="AA61" s="9">
-        <f>VLOOKUP($A61,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AB61" s="9">
-        <f>VLOOKUP($A61,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AC61" s="9">
-        <f>VLOOKUP($A61,$A$5:$J$34,9,FALSE)</f>
-        <v/>
-      </c>
+      <c r="AA61" s="13" t="n">
+        <v>46082</v>
+      </c>
+      <c r="AB61" s="13" t="n">
+        <v>46112</v>
+      </c>
+      <c r="AC61" s="9" t="n"/>
       <c r="AD61" s="9">
         <f>T61-AA61</f>
         <v/>
@@ -7139,18 +6888,13 @@
         <v>46112</v>
       </c>
       <c r="Y62" s="5" t="n"/>
-      <c r="AA62" s="9">
-        <f>VLOOKUP($A62,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AB62" s="9">
-        <f>VLOOKUP($A62,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AC62" s="9">
-        <f>VLOOKUP($A62,$A$5:$J$34,9,FALSE)</f>
-        <v/>
-      </c>
+      <c r="AA62" s="13" t="n">
+        <v>46082</v>
+      </c>
+      <c r="AB62" s="13" t="n">
+        <v>46112</v>
+      </c>
+      <c r="AC62" s="9" t="n"/>
       <c r="AD62" s="9">
         <f>T62-AA62</f>
         <v/>
@@ -7264,18 +7008,13 @@
         <v>46112</v>
       </c>
       <c r="Y63" s="5" t="n"/>
-      <c r="AA63" s="9">
-        <f>VLOOKUP($A63,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AB63" s="9">
-        <f>VLOOKUP($A63,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AC63" s="9">
-        <f>VLOOKUP($A63,$A$5:$J$34,9,FALSE)</f>
-        <v/>
-      </c>
+      <c r="AA63" s="13" t="n">
+        <v>46082</v>
+      </c>
+      <c r="AB63" s="13" t="n">
+        <v>46112</v>
+      </c>
+      <c r="AC63" s="9" t="n"/>
       <c r="AD63" s="9">
         <f>T63-AA63</f>
         <v/>
@@ -7389,18 +7128,13 @@
         <v>46112</v>
       </c>
       <c r="Y64" s="5" t="n"/>
-      <c r="AA64" s="9">
-        <f>VLOOKUP($A64,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AB64" s="9">
-        <f>VLOOKUP($A64,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AC64" s="9">
-        <f>VLOOKUP($A64,$A$5:$J$34,9,FALSE)</f>
-        <v/>
-      </c>
+      <c r="AA64" s="13" t="n">
+        <v>46082</v>
+      </c>
+      <c r="AB64" s="13" t="n">
+        <v>46112</v>
+      </c>
+      <c r="AC64" s="9" t="n"/>
       <c r="AD64" s="9">
         <f>T64-AA64</f>
         <v/>
@@ -7514,18 +7248,13 @@
         <v>46112</v>
       </c>
       <c r="Y65" s="5" t="n"/>
-      <c r="AA65" s="9">
-        <f>VLOOKUP($A65,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AB65" s="9">
-        <f>VLOOKUP($A65,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AC65" s="9">
-        <f>VLOOKUP($A65,$A$5:$J$34,9,FALSE)</f>
-        <v/>
-      </c>
+      <c r="AA65" s="13" t="n">
+        <v>46082</v>
+      </c>
+      <c r="AB65" s="13" t="n">
+        <v>46112</v>
+      </c>
+      <c r="AC65" s="9" t="n"/>
       <c r="AD65" s="9">
         <f>T65-AA65</f>
         <v/>
@@ -7639,18 +7368,13 @@
         <v>46112</v>
       </c>
       <c r="Y66" s="5" t="n"/>
-      <c r="AA66" s="9">
-        <f>VLOOKUP($A66,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AB66" s="9">
-        <f>VLOOKUP($A66,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AC66" s="9">
-        <f>VLOOKUP($A66,$A$5:$J$34,9,FALSE)</f>
-        <v/>
-      </c>
+      <c r="AA66" s="13" t="n">
+        <v>46082</v>
+      </c>
+      <c r="AB66" s="13" t="n">
+        <v>46112</v>
+      </c>
+      <c r="AC66" s="9" t="n"/>
       <c r="AD66" s="9">
         <f>T66-AA66</f>
         <v/>
@@ -7764,18 +7488,13 @@
         <v>46112</v>
       </c>
       <c r="Y67" s="5" t="n"/>
-      <c r="AA67" s="9">
-        <f>VLOOKUP($A67,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AB67" s="9">
-        <f>VLOOKUP($A67,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AC67" s="9">
-        <f>VLOOKUP($A67,$A$5:$J$34,9,FALSE)</f>
-        <v/>
-      </c>
+      <c r="AA67" s="13" t="n">
+        <v>46082</v>
+      </c>
+      <c r="AB67" s="13" t="n">
+        <v>46112</v>
+      </c>
+      <c r="AC67" s="9" t="n"/>
       <c r="AD67" s="9">
         <f>T67-AA67</f>
         <v/>
@@ -7889,18 +7608,13 @@
         <v>46112</v>
       </c>
       <c r="Y68" s="5" t="n"/>
-      <c r="AA68" s="9">
-        <f>VLOOKUP($A68,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AB68" s="9">
-        <f>VLOOKUP($A68,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AC68" s="9">
-        <f>VLOOKUP($A68,$A$5:$J$34,9,FALSE)</f>
-        <v/>
-      </c>
+      <c r="AA68" s="13" t="n">
+        <v>46082</v>
+      </c>
+      <c r="AB68" s="13" t="n">
+        <v>46112</v>
+      </c>
+      <c r="AC68" s="9" t="n"/>
       <c r="AD68" s="9">
         <f>T68-AA68</f>
         <v/>
@@ -8014,18 +7728,13 @@
         <v>46112</v>
       </c>
       <c r="Y69" s="5" t="n"/>
-      <c r="AA69" s="9">
-        <f>VLOOKUP($A69,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AB69" s="9">
-        <f>VLOOKUP($A69,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AC69" s="9">
-        <f>VLOOKUP($A69,$A$5:$J$34,9,FALSE)</f>
-        <v/>
-      </c>
+      <c r="AA69" s="13" t="n">
+        <v>46082</v>
+      </c>
+      <c r="AB69" s="13" t="n">
+        <v>46112</v>
+      </c>
+      <c r="AC69" s="9" t="n"/>
       <c r="AD69" s="9">
         <f>T69-AA69</f>
         <v/>
@@ -8139,18 +7848,13 @@
         <v>46112</v>
       </c>
       <c r="Y70" s="5" t="n"/>
-      <c r="AA70" s="9">
-        <f>VLOOKUP($A70,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AB70" s="9">
-        <f>VLOOKUP($A70,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AC70" s="9">
-        <f>VLOOKUP($A70,$A$5:$J$34,9,FALSE)</f>
-        <v/>
-      </c>
+      <c r="AA70" s="13" t="n">
+        <v>46082</v>
+      </c>
+      <c r="AB70" s="13" t="n">
+        <v>46112</v>
+      </c>
+      <c r="AC70" s="9" t="n"/>
       <c r="AD70" s="9">
         <f>T70-AA70</f>
         <v/>
@@ -8264,18 +7968,13 @@
         <v>46112</v>
       </c>
       <c r="Y71" s="5" t="n"/>
-      <c r="AA71" s="9">
-        <f>VLOOKUP($A71,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AB71" s="9">
-        <f>VLOOKUP($A71,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AC71" s="9">
-        <f>VLOOKUP($A71,$A$5:$J$34,9,FALSE)</f>
-        <v/>
-      </c>
+      <c r="AA71" s="13" t="n">
+        <v>46082</v>
+      </c>
+      <c r="AB71" s="13" t="n">
+        <v>46112</v>
+      </c>
+      <c r="AC71" s="9" t="n"/>
       <c r="AD71" s="9">
         <f>T71-AA71</f>
         <v/>
@@ -8389,18 +8088,13 @@
         <v>46112</v>
       </c>
       <c r="Y72" s="5" t="n"/>
-      <c r="AA72" s="9">
-        <f>VLOOKUP($A72,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AB72" s="9">
-        <f>VLOOKUP($A72,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AC72" s="9">
-        <f>VLOOKUP($A72,$A$5:$J$34,9,FALSE)</f>
-        <v/>
-      </c>
+      <c r="AA72" s="13" t="n">
+        <v>46082</v>
+      </c>
+      <c r="AB72" s="13" t="n">
+        <v>46112</v>
+      </c>
+      <c r="AC72" s="9" t="n"/>
       <c r="AD72" s="9">
         <f>T72-AA72</f>
         <v/>
@@ -8514,18 +8208,13 @@
         <v>46112</v>
       </c>
       <c r="Y73" s="5" t="n"/>
-      <c r="AA73" s="9">
-        <f>VLOOKUP($A73,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AB73" s="9">
-        <f>VLOOKUP($A73,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AC73" s="9">
-        <f>VLOOKUP($A73,$A$5:$J$34,9,FALSE)</f>
-        <v/>
-      </c>
+      <c r="AA73" s="13" t="n">
+        <v>46082</v>
+      </c>
+      <c r="AB73" s="13" t="n">
+        <v>46112</v>
+      </c>
+      <c r="AC73" s="9" t="n"/>
       <c r="AD73" s="9">
         <f>T73-AA73</f>
         <v/>
@@ -8639,18 +8328,13 @@
         <v>46112</v>
       </c>
       <c r="Y74" s="5" t="n"/>
-      <c r="AA74" s="9">
-        <f>VLOOKUP($A74,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AB74" s="9">
-        <f>VLOOKUP($A74,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AC74" s="9">
-        <f>VLOOKUP($A74,$A$5:$J$34,9,FALSE)</f>
-        <v/>
-      </c>
+      <c r="AA74" s="13" t="n">
+        <v>46082</v>
+      </c>
+      <c r="AB74" s="13" t="n">
+        <v>46112</v>
+      </c>
+      <c r="AC74" s="9" t="n"/>
       <c r="AD74" s="9">
         <f>T74-AA74</f>
         <v/>
@@ -8764,18 +8448,13 @@
         <v>46112</v>
       </c>
       <c r="Y75" s="5" t="n"/>
-      <c r="AA75" s="9">
-        <f>VLOOKUP($A75,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AB75" s="9">
-        <f>VLOOKUP($A75,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AC75" s="9">
-        <f>VLOOKUP($A75,$A$5:$J$34,9,FALSE)</f>
-        <v/>
-      </c>
+      <c r="AA75" s="13" t="n">
+        <v>46082</v>
+      </c>
+      <c r="AB75" s="13" t="n">
+        <v>46112</v>
+      </c>
+      <c r="AC75" s="9" t="n"/>
       <c r="AD75" s="9">
         <f>T75-AA75</f>
         <v/>
@@ -8889,18 +8568,13 @@
         <v>46112</v>
       </c>
       <c r="Y76" s="5" t="n"/>
-      <c r="AA76" s="9">
-        <f>VLOOKUP($A76,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AB76" s="9">
-        <f>VLOOKUP($A76,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AC76" s="9">
-        <f>VLOOKUP($A76,$A$5:$J$34,9,FALSE)</f>
-        <v/>
-      </c>
+      <c r="AA76" s="13" t="n">
+        <v>46082</v>
+      </c>
+      <c r="AB76" s="13" t="n">
+        <v>46112</v>
+      </c>
+      <c r="AC76" s="9" t="n"/>
       <c r="AD76" s="9">
         <f>T76-AA76</f>
         <v/>
@@ -9014,18 +8688,13 @@
         <v>46112</v>
       </c>
       <c r="Y77" s="5" t="n"/>
-      <c r="AA77" s="9">
-        <f>VLOOKUP($A77,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AB77" s="9">
-        <f>VLOOKUP($A77,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AC77" s="9">
-        <f>VLOOKUP($A77,$A$5:$J$34,9,FALSE)</f>
-        <v/>
-      </c>
+      <c r="AA77" s="13" t="n">
+        <v>46082</v>
+      </c>
+      <c r="AB77" s="13" t="n">
+        <v>46112</v>
+      </c>
+      <c r="AC77" s="9" t="n"/>
       <c r="AD77" s="9">
         <f>T77-AA77</f>
         <v/>
@@ -9139,18 +8808,13 @@
         <v>46112</v>
       </c>
       <c r="Y78" s="5" t="n"/>
-      <c r="AA78" s="9">
-        <f>VLOOKUP($A78,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AB78" s="9">
-        <f>VLOOKUP($A78,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AC78" s="9">
-        <f>VLOOKUP($A78,$A$5:$J$34,9,FALSE)</f>
-        <v/>
-      </c>
+      <c r="AA78" s="13" t="n">
+        <v>46082</v>
+      </c>
+      <c r="AB78" s="13" t="n">
+        <v>46112</v>
+      </c>
+      <c r="AC78" s="9" t="n"/>
       <c r="AD78" s="9">
         <f>T78-AA78</f>
         <v/>
@@ -9264,18 +8928,13 @@
         <v>46112</v>
       </c>
       <c r="Y79" s="5" t="n"/>
-      <c r="AA79" s="9">
-        <f>VLOOKUP($A79,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AB79" s="9">
-        <f>VLOOKUP($A79,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AC79" s="9">
-        <f>VLOOKUP($A79,$A$5:$J$34,9,FALSE)</f>
-        <v/>
-      </c>
+      <c r="AA79" s="13" t="n">
+        <v>46082</v>
+      </c>
+      <c r="AB79" s="13" t="n">
+        <v>46112</v>
+      </c>
+      <c r="AC79" s="9" t="n"/>
       <c r="AD79" s="9">
         <f>T79-AA79</f>
         <v/>
@@ -9389,18 +9048,13 @@
         <v>46112</v>
       </c>
       <c r="Y80" s="5" t="n"/>
-      <c r="AA80" s="9">
-        <f>VLOOKUP($A80,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AB80" s="9">
-        <f>VLOOKUP($A80,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AC80" s="9">
-        <f>VLOOKUP($A80,$A$5:$J$34,9,FALSE)</f>
-        <v/>
-      </c>
+      <c r="AA80" s="13" t="n">
+        <v>46082</v>
+      </c>
+      <c r="AB80" s="13" t="n">
+        <v>46112</v>
+      </c>
+      <c r="AC80" s="9" t="n"/>
       <c r="AD80" s="9">
         <f>T80-AA80</f>
         <v/>
@@ -9514,18 +9168,13 @@
         <v>46112</v>
       </c>
       <c r="Y81" s="5" t="n"/>
-      <c r="AA81" s="9">
-        <f>VLOOKUP($A81,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AB81" s="9">
-        <f>VLOOKUP($A81,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AC81" s="9">
-        <f>VLOOKUP($A81,$A$5:$J$34,9,FALSE)</f>
-        <v/>
-      </c>
+      <c r="AA81" s="13" t="n">
+        <v>46082</v>
+      </c>
+      <c r="AB81" s="13" t="n">
+        <v>46112</v>
+      </c>
+      <c r="AC81" s="9" t="n"/>
       <c r="AD81" s="9">
         <f>T81-AA81</f>
         <v/>
@@ -9639,18 +9288,13 @@
         <v>46112</v>
       </c>
       <c r="Y82" s="5" t="n"/>
-      <c r="AA82" s="9">
-        <f>VLOOKUP($A82,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AB82" s="9">
-        <f>VLOOKUP($A82,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AC82" s="9">
-        <f>VLOOKUP($A82,$A$5:$J$34,9,FALSE)</f>
-        <v/>
-      </c>
+      <c r="AA82" s="13" t="n">
+        <v>46082</v>
+      </c>
+      <c r="AB82" s="13" t="n">
+        <v>46112</v>
+      </c>
+      <c r="AC82" s="9" t="n"/>
       <c r="AD82" s="9">
         <f>T82-AA82</f>
         <v/>
@@ -9764,18 +9408,13 @@
         <v>46112</v>
       </c>
       <c r="Y83" s="5" t="n"/>
-      <c r="AA83" s="9">
-        <f>VLOOKUP($A83,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AB83" s="9">
-        <f>VLOOKUP($A83,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AC83" s="9">
-        <f>VLOOKUP($A83,$A$5:$J$34,9,FALSE)</f>
-        <v/>
-      </c>
+      <c r="AA83" s="13" t="n">
+        <v>46082</v>
+      </c>
+      <c r="AB83" s="13" t="n">
+        <v>46112</v>
+      </c>
+      <c r="AC83" s="9" t="n"/>
       <c r="AD83" s="9">
         <f>T83-AA83</f>
         <v/>
@@ -9889,18 +9528,13 @@
         <v>46112</v>
       </c>
       <c r="Y84" s="5" t="n"/>
-      <c r="AA84" s="9">
-        <f>VLOOKUP($A84,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AB84" s="9">
-        <f>VLOOKUP($A84,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AC84" s="9">
-        <f>VLOOKUP($A84,$A$5:$J$34,9,FALSE)</f>
-        <v/>
-      </c>
+      <c r="AA84" s="13" t="n">
+        <v>46082</v>
+      </c>
+      <c r="AB84" s="13" t="n">
+        <v>46112</v>
+      </c>
+      <c r="AC84" s="9" t="n"/>
       <c r="AD84" s="9">
         <f>T84-AA84</f>
         <v/>
@@ -10014,18 +9648,13 @@
         <v>46112</v>
       </c>
       <c r="Y85" s="5" t="n"/>
-      <c r="AA85" s="9">
-        <f>VLOOKUP($A85,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AB85" s="9">
-        <f>VLOOKUP($A85,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AC85" s="9">
-        <f>VLOOKUP($A85,$A$5:$J$34,9,FALSE)</f>
-        <v/>
-      </c>
+      <c r="AA85" s="13" t="n">
+        <v>46082</v>
+      </c>
+      <c r="AB85" s="13" t="n">
+        <v>46112</v>
+      </c>
+      <c r="AC85" s="9" t="n"/>
       <c r="AD85" s="9">
         <f>T85-AA85</f>
         <v/>
@@ -10139,18 +9768,13 @@
         <v>46112</v>
       </c>
       <c r="Y86" s="5" t="n"/>
-      <c r="AA86" s="9">
-        <f>VLOOKUP($A86,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AB86" s="9">
-        <f>VLOOKUP($A86,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AC86" s="9">
-        <f>VLOOKUP($A86,$A$5:$J$34,9,FALSE)</f>
-        <v/>
-      </c>
+      <c r="AA86" s="13" t="n">
+        <v>46082</v>
+      </c>
+      <c r="AB86" s="13" t="n">
+        <v>46112</v>
+      </c>
+      <c r="AC86" s="9" t="n"/>
       <c r="AD86" s="9">
         <f>T86-AA86</f>
         <v/>
@@ -10264,18 +9888,13 @@
         <v>46112</v>
       </c>
       <c r="Y87" s="5" t="n"/>
-      <c r="AA87" s="9">
-        <f>VLOOKUP($A87,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AB87" s="9">
-        <f>VLOOKUP($A87,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AC87" s="9">
-        <f>VLOOKUP($A87,$A$5:$J$34,9,FALSE)</f>
-        <v/>
-      </c>
+      <c r="AA87" s="13" t="n">
+        <v>46082</v>
+      </c>
+      <c r="AB87" s="13" t="n">
+        <v>46112</v>
+      </c>
+      <c r="AC87" s="9" t="n"/>
       <c r="AD87" s="9">
         <f>T87-AA87</f>
         <v/>
@@ -10389,18 +10008,13 @@
         <v>46112</v>
       </c>
       <c r="Y88" s="5" t="n"/>
-      <c r="AA88" s="9">
-        <f>VLOOKUP($A88,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AB88" s="9">
-        <f>VLOOKUP($A88,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AC88" s="9">
-        <f>VLOOKUP($A88,$A$5:$J$34,9,FALSE)</f>
-        <v/>
-      </c>
+      <c r="AA88" s="13" t="n">
+        <v>46082</v>
+      </c>
+      <c r="AB88" s="13" t="n">
+        <v>46112</v>
+      </c>
+      <c r="AC88" s="9" t="n"/>
       <c r="AD88" s="9">
         <f>T88-AA88</f>
         <v/>
@@ -10514,18 +10128,13 @@
         <v>46112</v>
       </c>
       <c r="Y89" s="5" t="n"/>
-      <c r="AA89" s="9">
-        <f>VLOOKUP($A89,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AB89" s="9">
-        <f>VLOOKUP($A89,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AC89" s="9">
-        <f>VLOOKUP($A89,$A$5:$J$34,9,FALSE)</f>
-        <v/>
-      </c>
+      <c r="AA89" s="13" t="n">
+        <v>46082</v>
+      </c>
+      <c r="AB89" s="13" t="n">
+        <v>46112</v>
+      </c>
+      <c r="AC89" s="9" t="n"/>
       <c r="AD89" s="9">
         <f>T89-AA89</f>
         <v/>
@@ -10639,18 +10248,13 @@
         <v>46112</v>
       </c>
       <c r="Y90" s="5" t="n"/>
-      <c r="AA90" s="9">
-        <f>VLOOKUP($A90,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AB90" s="9">
-        <f>VLOOKUP($A90,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AC90" s="9">
-        <f>VLOOKUP($A90,$A$5:$J$34,9,FALSE)</f>
-        <v/>
-      </c>
+      <c r="AA90" s="13" t="n">
+        <v>46082</v>
+      </c>
+      <c r="AB90" s="13" t="n">
+        <v>46112</v>
+      </c>
+      <c r="AC90" s="9" t="n"/>
       <c r="AD90" s="9">
         <f>T90-AA90</f>
         <v/>
@@ -10764,18 +10368,13 @@
         <v>46112</v>
       </c>
       <c r="Y91" s="5" t="n"/>
-      <c r="AA91" s="9">
-        <f>VLOOKUP($A91,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AB91" s="9">
-        <f>VLOOKUP($A91,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AC91" s="9">
-        <f>VLOOKUP($A91,$A$5:$J$34,9,FALSE)</f>
-        <v/>
-      </c>
+      <c r="AA91" s="13" t="n">
+        <v>46082</v>
+      </c>
+      <c r="AB91" s="13" t="n">
+        <v>46112</v>
+      </c>
+      <c r="AC91" s="9" t="n"/>
       <c r="AD91" s="9">
         <f>T91-AA91</f>
         <v/>
@@ -10889,18 +10488,13 @@
         <v>46112</v>
       </c>
       <c r="Y92" s="5" t="n"/>
-      <c r="AA92" s="9">
-        <f>VLOOKUP($A92,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AB92" s="9">
-        <f>VLOOKUP($A92,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AC92" s="9">
-        <f>VLOOKUP($A92,$A$5:$J$34,9,FALSE)</f>
-        <v/>
-      </c>
+      <c r="AA92" s="13" t="n">
+        <v>46082</v>
+      </c>
+      <c r="AB92" s="13" t="n">
+        <v>46112</v>
+      </c>
+      <c r="AC92" s="9" t="n"/>
       <c r="AD92" s="9">
         <f>T92-AA92</f>
         <v/>
@@ -11014,18 +10608,13 @@
         <v>46112</v>
       </c>
       <c r="Y93" s="5" t="n"/>
-      <c r="AA93" s="9">
-        <f>VLOOKUP($A93,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AB93" s="9">
-        <f>VLOOKUP($A93,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AC93" s="9">
-        <f>VLOOKUP($A93,$A$5:$J$34,9,FALSE)</f>
-        <v/>
-      </c>
+      <c r="AA93" s="13" t="n">
+        <v>46082</v>
+      </c>
+      <c r="AB93" s="13" t="n">
+        <v>46112</v>
+      </c>
+      <c r="AC93" s="9" t="n"/>
       <c r="AD93" s="9">
         <f>T93-AA93</f>
         <v/>
@@ -11139,18 +10728,13 @@
         <v>46112</v>
       </c>
       <c r="Y94" s="5" t="n"/>
-      <c r="AA94" s="9">
-        <f>VLOOKUP($A94,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AB94" s="9">
-        <f>VLOOKUP($A94,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AC94" s="9">
-        <f>VLOOKUP($A94,$A$5:$J$34,9,FALSE)</f>
-        <v/>
-      </c>
+      <c r="AA94" s="13" t="n">
+        <v>46082</v>
+      </c>
+      <c r="AB94" s="13" t="n">
+        <v>46112</v>
+      </c>
+      <c r="AC94" s="9" t="n"/>
       <c r="AD94" s="9">
         <f>T94-AA94</f>
         <v/>
@@ -11264,18 +10848,13 @@
         <v>46112</v>
       </c>
       <c r="Y95" s="5" t="n"/>
-      <c r="AA95" s="9">
-        <f>VLOOKUP($A95,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AB95" s="9">
-        <f>VLOOKUP($A95,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AC95" s="9">
-        <f>VLOOKUP($A95,$A$5:$J$34,9,FALSE)</f>
-        <v/>
-      </c>
+      <c r="AA95" s="13" t="n">
+        <v>46082</v>
+      </c>
+      <c r="AB95" s="13" t="n">
+        <v>46112</v>
+      </c>
+      <c r="AC95" s="9" t="n"/>
       <c r="AD95" s="9">
         <f>T95-AA95</f>
         <v/>
@@ -11389,18 +10968,13 @@
         <v>46112</v>
       </c>
       <c r="Y96" s="5" t="n"/>
-      <c r="AA96" s="9">
-        <f>VLOOKUP($A96,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AB96" s="9">
-        <f>VLOOKUP($A96,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AC96" s="9">
-        <f>VLOOKUP($A96,$A$5:$J$34,9,FALSE)</f>
-        <v/>
-      </c>
+      <c r="AA96" s="13" t="n">
+        <v>46082</v>
+      </c>
+      <c r="AB96" s="13" t="n">
+        <v>46112</v>
+      </c>
+      <c r="AC96" s="9" t="n"/>
       <c r="AD96" s="9">
         <f>T96-AA96</f>
         <v/>
@@ -11514,18 +11088,13 @@
         <v>46112</v>
       </c>
       <c r="Y97" s="5" t="n"/>
-      <c r="AA97" s="9">
-        <f>VLOOKUP($A97,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AB97" s="9">
-        <f>VLOOKUP($A97,$A$5:$J$34,8,FALSE)</f>
-        <v/>
-      </c>
-      <c r="AC97" s="9">
-        <f>VLOOKUP($A97,$A$5:$J$34,9,FALSE)</f>
-        <v/>
-      </c>
+      <c r="AA97" s="13" t="n">
+        <v>46082</v>
+      </c>
+      <c r="AB97" s="13" t="n">
+        <v>46112</v>
+      </c>
+      <c r="AC97" s="9" t="n"/>
       <c r="AD97" s="9">
         <f>T97-AA97</f>
         <v/>
